--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A54FC155-164F-4C39-BA6F-5A7F08AF2302}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D24EFDC-37A8-4613-9DAC-EFE3CB9E398B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -93,6 +93,51 @@
   </si>
   <si>
     <t>Telefono</t>
+  </si>
+  <si>
+    <t>luca</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>Guglielmi</t>
+  </si>
+  <si>
+    <t>Key Account Manager - Intrologistics &amp; Adherence Solutions (PDC &amp; PPC)</t>
+  </si>
+  <si>
+    <t>luca.guglielmi@bd.com</t>
+  </si>
+  <si>
+    <t>Mirko</t>
+  </si>
+  <si>
+    <t>De Miere</t>
+  </si>
+  <si>
+    <t>mirko</t>
+  </si>
+  <si>
+    <t>Sales Consultant Sud Italia</t>
+  </si>
+  <si>
+    <t>mirko.de.miere@bd.com</t>
+  </si>
+  <si>
+    <t>andrea</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Speziale</t>
+  </si>
+  <si>
+    <t>Inside Sales Rapresentative</t>
+  </si>
+  <si>
+    <t>andrea.speziale@bd.com</t>
   </si>
 </sst>
 </file>
@@ -156,6 +201,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,14 +524,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
   </cols>
@@ -556,10 +605,82 @@
         <v>11</v>
       </c>
     </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>3666437392</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>3482269711</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>3455964602</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{354C76A4-C239-4F2F-AF96-C61038D4F751}"/>
     <hyperlink ref="G2" r:id="rId2" xr:uid="{EE366E73-902C-4325-A83A-A271D5FDE230}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{8A1BEC5C-D997-4752-972A-D72F012F269D}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{E0477FB2-FB22-4605-B636-BA0D3F850DA6}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{4490178C-AF8C-4778-BCB2-7797EC81C6F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D24EFDC-37A8-4613-9DAC-EFE3CB9E398B}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{893634C2-8FE2-49BD-B4A3-6A45C3C74B17}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -138,6 +138,21 @@
   </si>
   <si>
     <t>andrea.speziale@bd.com</t>
+  </si>
+  <si>
+    <t>antonello</t>
+  </si>
+  <si>
+    <t>Antonello</t>
+  </si>
+  <si>
+    <t>Capriglione</t>
+  </si>
+  <si>
+    <t>Area Service Manager</t>
+  </si>
+  <si>
+    <t>antonello.capriglione@bd.com</t>
   </si>
 </sst>
 </file>
@@ -201,10 +216,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,12 +535,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
@@ -674,6 +685,29 @@
         <v>33</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>3426937297</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{354C76A4-C239-4F2F-AF96-C61038D4F751}"/>
@@ -681,6 +715,7 @@
     <hyperlink ref="G4" r:id="rId3" xr:uid="{8A1BEC5C-D997-4752-972A-D72F012F269D}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{E0477FB2-FB22-4605-B636-BA0D3F850DA6}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{4490178C-AF8C-4778-BCB2-7797EC81C6F9}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{D278CE78-14AB-4BBD-BB4B-439D56D051D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{893634C2-8FE2-49BD-B4A3-6A45C3C74B17}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357E548A-14AF-4565-A718-5057AF75C456}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -153,6 +153,39 @@
   </si>
   <si>
     <t>antonello.capriglione@bd.com</t>
+  </si>
+  <si>
+    <t>fulvio</t>
+  </si>
+  <si>
+    <t>Fulvio</t>
+  </si>
+  <si>
+    <t>Di Muro</t>
+  </si>
+  <si>
+    <t>NEULAB</t>
+  </si>
+  <si>
+    <t>Senior Sales Advisor</t>
+  </si>
+  <si>
+    <t>fulvio.dimuro@neulab.io</t>
+  </si>
+  <si>
+    <t>simone</t>
+  </si>
+  <si>
+    <t>Simone</t>
+  </si>
+  <si>
+    <t>Caddeo</t>
+  </si>
+  <si>
+    <t>Resp. Comm. Centro Italia</t>
+  </si>
+  <si>
+    <t>simone.caddeo@bd.com</t>
   </si>
 </sst>
 </file>
@@ -216,6 +249,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -708,6 +745,52 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8">
+        <v>3939408291</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9">
+        <v>3357940182</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{354C76A4-C239-4F2F-AF96-C61038D4F751}"/>
@@ -716,6 +799,8 @@
     <hyperlink ref="G5" r:id="rId4" xr:uid="{E0477FB2-FB22-4605-B636-BA0D3F850DA6}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{4490178C-AF8C-4778-BCB2-7797EC81C6F9}"/>
     <hyperlink ref="G7" r:id="rId6" xr:uid="{D278CE78-14AB-4BBD-BB4B-439D56D051D3}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{127379AC-1F79-4666-AD51-AE614782034F}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{93ED8E35-663E-4440-891E-950B27A501C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357E548A-14AF-4565-A718-5057AF75C456}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2E7CF5-3809-4BF7-817D-07960A7291A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
   <si>
     <t>ID</t>
   </si>
@@ -186,6 +186,21 @@
   </si>
   <si>
     <t>simone.caddeo@bd.com</t>
+  </si>
+  <si>
+    <t>paolo</t>
+  </si>
+  <si>
+    <t>Paolo</t>
+  </si>
+  <si>
+    <t>D'Ecclesis</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>paolo.decclesis@bd.com</t>
   </si>
 </sst>
 </file>
@@ -572,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -791,6 +806,29 @@
         <v>49</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10">
+        <v>3450926082</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{354C76A4-C239-4F2F-AF96-C61038D4F751}"/>
@@ -801,6 +839,7 @@
     <hyperlink ref="G7" r:id="rId6" xr:uid="{D278CE78-14AB-4BBD-BB4B-439D56D051D3}"/>
     <hyperlink ref="G8" r:id="rId7" xr:uid="{127379AC-1F79-4666-AD51-AE614782034F}"/>
     <hyperlink ref="G9" r:id="rId8" xr:uid="{93ED8E35-663E-4440-891E-950B27A501C3}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{B54B5112-A906-48F8-98AF-824BFA7D028B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2E7CF5-3809-4BF7-817D-07960A7291A6}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CF91783-EBE5-410B-8C1A-BB37629A32FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -197,10 +197,10 @@
     <t>D'Ecclesis</t>
   </si>
   <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
     <t>paolo.decclesis@bd.com</t>
+  </si>
+  <si>
+    <t>Senior Project Manager</t>
   </si>
 </sst>
 </file>
@@ -820,13 +820,13 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>3450926082</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CF91783-EBE5-410B-8C1A-BB37629A32FC}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C294562-AE38-4573-9F04-D721EC4656C5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,36 @@
   </si>
   <si>
     <t>Senior Project Manager</t>
+  </si>
+  <si>
+    <t>alessandro</t>
+  </si>
+  <si>
+    <t>Alessandro</t>
+  </si>
+  <si>
+    <t>Raciti</t>
+  </si>
+  <si>
+    <t>RB Solutions</t>
+  </si>
+  <si>
+    <t>Cofondatore</t>
+  </si>
+  <si>
+    <t>alessandro.raciti@rbsolutions.it</t>
+  </si>
+  <si>
+    <t>lucia.boncori@rbsolutions.it</t>
+  </si>
+  <si>
+    <t>Lucia</t>
+  </si>
+  <si>
+    <t>lucia</t>
+  </si>
+  <si>
+    <t>Boncori</t>
   </si>
 </sst>
 </file>
@@ -587,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -829,6 +859,52 @@
         <v>53</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11">
+        <v>3450919729</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12">
+        <v>3926703115</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{354C76A4-C239-4F2F-AF96-C61038D4F751}"/>
@@ -840,6 +916,8 @@
     <hyperlink ref="G8" r:id="rId7" xr:uid="{127379AC-1F79-4666-AD51-AE614782034F}"/>
     <hyperlink ref="G9" r:id="rId8" xr:uid="{93ED8E35-663E-4440-891E-950B27A501C3}"/>
     <hyperlink ref="G10" r:id="rId9" xr:uid="{B54B5112-A906-48F8-98AF-824BFA7D028B}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{E702948F-C7C0-457E-A94E-B8EF77D27D8C}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{18BBE455-BEC6-4132-91B9-21D84B8FD2A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/team.xlsx
+++ b/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6564512f1116c503/Documents/Team vcard per tag/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C294562-AE38-4573-9F04-D721EC4656C5}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{DB41A044-4BC9-4AF2-B6C0-3874D41278A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D936EBE2-526A-47AB-97EF-E2B69404CAAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{025CBAD7-7C99-48E9-893F-A13F7915EA8A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -231,6 +231,24 @@
   </si>
   <si>
     <t>Boncori</t>
+  </si>
+  <si>
+    <t>beppe</t>
+  </si>
+  <si>
+    <t>Beppe</t>
+  </si>
+  <si>
+    <t>Ruggieri</t>
+  </si>
+  <si>
+    <t>Direttore Rete Vendite</t>
+  </si>
+  <si>
+    <t>Pharmaservice Srl</t>
+  </si>
+  <si>
+    <t>beppe.ruggieri@pharmaservice.it</t>
   </si>
 </sst>
 </file>
@@ -617,16 +635,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D909670F-70CD-473A-BB06-2B658ECBDFD6}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -903,6 +921,29 @@
       </c>
       <c r="G12" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>3476132881</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -918,6 +959,7 @@
     <hyperlink ref="G10" r:id="rId9" xr:uid="{B54B5112-A906-48F8-98AF-824BFA7D028B}"/>
     <hyperlink ref="G11" r:id="rId10" xr:uid="{E702948F-C7C0-457E-A94E-B8EF77D27D8C}"/>
     <hyperlink ref="G12" r:id="rId11" xr:uid="{18BBE455-BEC6-4132-91B9-21D84B8FD2A5}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{8934ABF5-954C-48D8-A2F4-FD069DA06267}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
